--- a/artfynd/A 9438-2025 artfynd.xlsx
+++ b/artfynd/A 9438-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956518</v>
       </c>
       <c r="B2" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136956521</v>
       </c>
       <c r="B3" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136956524</v>
       </c>
       <c r="B4" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136956528</v>
       </c>
       <c r="B5" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136956531</v>
       </c>
       <c r="B6" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136956535</v>
       </c>
       <c r="B7" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 9438-2025 artfynd.xlsx
+++ b/artfynd/A 9438-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956518</v>
       </c>
       <c r="B2" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136956521</v>
       </c>
       <c r="B3" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136956524</v>
       </c>
       <c r="B4" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136956528</v>
       </c>
       <c r="B5" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136956531</v>
       </c>
       <c r="B6" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136956535</v>
       </c>
       <c r="B7" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 9438-2025 artfynd.xlsx
+++ b/artfynd/A 9438-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956518</v>
       </c>
       <c r="B2" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136956521</v>
       </c>
       <c r="B3" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136956524</v>
       </c>
       <c r="B4" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136956528</v>
       </c>
       <c r="B5" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136956531</v>
       </c>
       <c r="B6" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136956535</v>
       </c>
       <c r="B7" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 9438-2025 artfynd.xlsx
+++ b/artfynd/A 9438-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956518</v>
       </c>
       <c r="B2" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136956521</v>
       </c>
       <c r="B3" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136956524</v>
       </c>
       <c r="B4" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136956528</v>
       </c>
       <c r="B5" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136956531</v>
       </c>
       <c r="B6" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136956535</v>
       </c>
       <c r="B7" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 9438-2025 artfynd.xlsx
+++ b/artfynd/A 9438-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956518</v>
       </c>
       <c r="B2" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136956521</v>
       </c>
       <c r="B3" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136956524</v>
       </c>
       <c r="B4" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136956528</v>
       </c>
       <c r="B5" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136956531</v>
       </c>
       <c r="B6" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136956535</v>
       </c>
       <c r="B7" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 9438-2025 artfynd.xlsx
+++ b/artfynd/A 9438-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956518</v>
       </c>
       <c r="B2" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136956521</v>
       </c>
       <c r="B3" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136956524</v>
       </c>
       <c r="B4" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136956528</v>
       </c>
       <c r="B5" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136956531</v>
       </c>
       <c r="B6" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136956535</v>
       </c>
       <c r="B7" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 9438-2025 artfynd.xlsx
+++ b/artfynd/A 9438-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956518</v>
       </c>
       <c r="B2" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136956521</v>
       </c>
       <c r="B3" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136956524</v>
       </c>
       <c r="B4" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136956528</v>
       </c>
       <c r="B5" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136956531</v>
       </c>
       <c r="B6" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136956535</v>
       </c>
       <c r="B7" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 9438-2025 artfynd.xlsx
+++ b/artfynd/A 9438-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956518</v>
       </c>
       <c r="B2" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136956521</v>
       </c>
       <c r="B3" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136956524</v>
       </c>
       <c r="B4" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136956528</v>
       </c>
       <c r="B5" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136956531</v>
       </c>
       <c r="B6" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136956535</v>
       </c>
       <c r="B7" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 9438-2025 artfynd.xlsx
+++ b/artfynd/A 9438-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956518</v>
       </c>
       <c r="B2" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136956521</v>
       </c>
       <c r="B3" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136956524</v>
       </c>
       <c r="B4" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136956528</v>
       </c>
       <c r="B5" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136956531</v>
       </c>
       <c r="B6" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136956535</v>
       </c>
       <c r="B7" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 9438-2025 artfynd.xlsx
+++ b/artfynd/A 9438-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956518</v>
       </c>
       <c r="B2" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136956521</v>
       </c>
       <c r="B3" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136956524</v>
       </c>
       <c r="B4" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136956528</v>
       </c>
       <c r="B5" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136956531</v>
       </c>
       <c r="B6" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136956535</v>
       </c>
       <c r="B7" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 9438-2025 artfynd.xlsx
+++ b/artfynd/A 9438-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956518</v>
       </c>
       <c r="B2" t="n">
-        <v>110113</v>
+        <v>110134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136956521</v>
       </c>
       <c r="B3" t="n">
-        <v>110113</v>
+        <v>110134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136956524</v>
       </c>
       <c r="B4" t="n">
-        <v>110113</v>
+        <v>110134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136956528</v>
       </c>
       <c r="B5" t="n">
-        <v>110113</v>
+        <v>110134</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136956531</v>
       </c>
       <c r="B6" t="n">
-        <v>110113</v>
+        <v>110134</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136956535</v>
       </c>
       <c r="B7" t="n">
-        <v>110113</v>
+        <v>110134</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 9438-2025 artfynd.xlsx
+++ b/artfynd/A 9438-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956518</v>
       </c>
       <c r="B2" t="n">
-        <v>110134</v>
+        <v>110135</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136956521</v>
       </c>
       <c r="B3" t="n">
-        <v>110134</v>
+        <v>110135</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136956524</v>
       </c>
       <c r="B4" t="n">
-        <v>110134</v>
+        <v>110135</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136956528</v>
       </c>
       <c r="B5" t="n">
-        <v>110134</v>
+        <v>110135</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136956531</v>
       </c>
       <c r="B6" t="n">
-        <v>110134</v>
+        <v>110135</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136956535</v>
       </c>
       <c r="B7" t="n">
-        <v>110134</v>
+        <v>110135</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 9438-2025 artfynd.xlsx
+++ b/artfynd/A 9438-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956518</v>
       </c>
       <c r="B2" t="n">
-        <v>110135</v>
+        <v>110140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136956521</v>
       </c>
       <c r="B3" t="n">
-        <v>110135</v>
+        <v>110140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136956524</v>
       </c>
       <c r="B4" t="n">
-        <v>110135</v>
+        <v>110140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136956528</v>
       </c>
       <c r="B5" t="n">
-        <v>110135</v>
+        <v>110140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136956531</v>
       </c>
       <c r="B6" t="n">
-        <v>110135</v>
+        <v>110140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136956535</v>
       </c>
       <c r="B7" t="n">
-        <v>110135</v>
+        <v>110140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 9438-2025 artfynd.xlsx
+++ b/artfynd/A 9438-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956518</v>
       </c>
       <c r="B2" t="n">
-        <v>110140</v>
+        <v>110143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136956521</v>
       </c>
       <c r="B3" t="n">
-        <v>110140</v>
+        <v>110143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136956524</v>
       </c>
       <c r="B4" t="n">
-        <v>110140</v>
+        <v>110143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136956528</v>
       </c>
       <c r="B5" t="n">
-        <v>110140</v>
+        <v>110143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136956531</v>
       </c>
       <c r="B6" t="n">
-        <v>110140</v>
+        <v>110143</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136956535</v>
       </c>
       <c r="B7" t="n">
-        <v>110140</v>
+        <v>110143</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 9438-2025 artfynd.xlsx
+++ b/artfynd/A 9438-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956518</v>
       </c>
       <c r="B2" t="n">
-        <v>110143</v>
+        <v>110149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136956521</v>
       </c>
       <c r="B3" t="n">
-        <v>110143</v>
+        <v>110149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136956524</v>
       </c>
       <c r="B4" t="n">
-        <v>110143</v>
+        <v>110149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136956528</v>
       </c>
       <c r="B5" t="n">
-        <v>110143</v>
+        <v>110149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136956531</v>
       </c>
       <c r="B6" t="n">
-        <v>110143</v>
+        <v>110149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136956535</v>
       </c>
       <c r="B7" t="n">
-        <v>110143</v>
+        <v>110149</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 9438-2025 artfynd.xlsx
+++ b/artfynd/A 9438-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956518</v>
       </c>
       <c r="B2" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136956521</v>
       </c>
       <c r="B3" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136956524</v>
       </c>
       <c r="B4" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136956528</v>
       </c>
       <c r="B5" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136956531</v>
       </c>
       <c r="B6" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136956535</v>
       </c>
       <c r="B7" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 9438-2025 artfynd.xlsx
+++ b/artfynd/A 9438-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956518</v>
       </c>
       <c r="B2" t="n">
-        <v>110150</v>
+        <v>110162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136956521</v>
       </c>
       <c r="B3" t="n">
-        <v>110150</v>
+        <v>110162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136956524</v>
       </c>
       <c r="B4" t="n">
-        <v>110150</v>
+        <v>110162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136956528</v>
       </c>
       <c r="B5" t="n">
-        <v>110150</v>
+        <v>110162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136956531</v>
       </c>
       <c r="B6" t="n">
-        <v>110150</v>
+        <v>110162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136956535</v>
       </c>
       <c r="B7" t="n">
-        <v>110150</v>
+        <v>110162</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 9438-2025 artfynd.xlsx
+++ b/artfynd/A 9438-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956518</v>
       </c>
       <c r="B2" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136956521</v>
       </c>
       <c r="B3" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136956524</v>
       </c>
       <c r="B4" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136956528</v>
       </c>
       <c r="B5" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136956531</v>
       </c>
       <c r="B6" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136956535</v>
       </c>
       <c r="B7" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 9438-2025 artfynd.xlsx
+++ b/artfynd/A 9438-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956518</v>
       </c>
       <c r="B2" t="n">
-        <v>110163</v>
+        <v>110166</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136956521</v>
       </c>
       <c r="B3" t="n">
-        <v>110163</v>
+        <v>110166</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136956524</v>
       </c>
       <c r="B4" t="n">
-        <v>110163</v>
+        <v>110166</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136956528</v>
       </c>
       <c r="B5" t="n">
-        <v>110163</v>
+        <v>110166</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136956531</v>
       </c>
       <c r="B6" t="n">
-        <v>110163</v>
+        <v>110166</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136956535</v>
       </c>
       <c r="B7" t="n">
-        <v>110163</v>
+        <v>110166</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 9438-2025 artfynd.xlsx
+++ b/artfynd/A 9438-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956518</v>
       </c>
       <c r="B2" t="n">
-        <v>110166</v>
+        <v>110168</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136956521</v>
       </c>
       <c r="B3" t="n">
-        <v>110166</v>
+        <v>110168</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136956524</v>
       </c>
       <c r="B4" t="n">
-        <v>110166</v>
+        <v>110168</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136956528</v>
       </c>
       <c r="B5" t="n">
-        <v>110166</v>
+        <v>110168</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136956531</v>
       </c>
       <c r="B6" t="n">
-        <v>110166</v>
+        <v>110168</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136956535</v>
       </c>
       <c r="B7" t="n">
-        <v>110166</v>
+        <v>110168</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 9438-2025 artfynd.xlsx
+++ b/artfynd/A 9438-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956518</v>
       </c>
       <c r="B2" t="n">
-        <v>110168</v>
+        <v>110172</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136956521</v>
       </c>
       <c r="B3" t="n">
-        <v>110168</v>
+        <v>110172</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136956524</v>
       </c>
       <c r="B4" t="n">
-        <v>110168</v>
+        <v>110172</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136956528</v>
       </c>
       <c r="B5" t="n">
-        <v>110168</v>
+        <v>110172</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136956531</v>
       </c>
       <c r="B6" t="n">
-        <v>110168</v>
+        <v>110172</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136956535</v>
       </c>
       <c r="B7" t="n">
-        <v>110168</v>
+        <v>110172</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
